--- a/inputs/data_symbols_TD/06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5.xlsx
+++ b/inputs/data_symbols_TD/06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_TD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED872205-7D81-48D3-800E-09F5FFB477FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{02C7D87B-129B-46A0-BC07-668A259C7AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4155" yWindow="495" windowWidth="18900" windowHeight="11100" xr2:uid="{C1770917-7869-496D-9FC8-DCC548892A09}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{D7F115AD-0F5A-4AAB-AC4E-6E3DEBC4ACB3}"/>
   </bookViews>
   <sheets>
     <sheet name="06_LTAN06_800km_1213COLD_PX_STT" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C5546B2-15D4-4E36-BAD6-20C4A4DF4AD1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{221BCED9-6F4A-4BC4-8A3E-E1592802C4E3}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/inputs/data_symbols_TD/06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5.xlsx
+++ b/inputs/data_symbols_TD/06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02C7D87B-129B-46A0-BC07-668A259C7AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{54C6E577-4E36-43D0-BF7E-F78810A78116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{D7F115AD-0F5A-4AAB-AC4E-6E3DEBC4ACB3}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{318F9C05-CB7A-4F9A-B260-76030DFDF66D}"/>
   </bookViews>
   <sheets>
     <sheet name="06_LTAN06_800km_1213COLD_PX_STT" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{221BCED9-6F4A-4BC4-8A3E-E1592802C4E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0162C8EE-22EF-4229-B1FC-ABF5E6DC8A15}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>43.087690000000002</v>
+        <v>43.115729999999999</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>43.087690000000002</v>
+        <v>43.115729999999999</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>43.334690000000002</v>
+        <v>43.361229999999999</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>43.554870000000001</v>
+        <v>43.581359999999997</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>43.75611</v>
+        <v>43.783470000000001</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>43.944009999999999</v>
+        <v>43.971980000000002</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>44.12182</v>
+        <v>44.149920000000002</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>44.291460000000001</v>
+        <v>44.319360000000003</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -1143,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>44.454900000000002</v>
+        <v>44.482059999999997</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>44.61318</v>
+        <v>44.639270000000003</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -1171,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>44.766919999999999</v>
+        <v>44.792000000000002</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>44.916170000000001</v>
+        <v>44.941459999999999</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>45.061720000000001</v>
+        <v>45.087829999999997</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>45.204349999999998</v>
+        <v>45.231439999999999</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>45.344670000000001</v>
+        <v>45.372540000000001</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>45.482590000000002</v>
+        <v>45.511130000000001</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>45.617750000000001</v>
+        <v>45.646529999999998</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
@@ -1269,7 +1269,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>45.75009</v>
+        <v>45.77861</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>45.879829999999998</v>
+        <v>45.907809999999998</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
@@ -1297,7 +1297,7 @@
         <v>3</v>
       </c>
       <c r="D21">
-        <v>44.458469999999998</v>
+        <v>44.494430000000001</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
@@ -1311,7 +1311,7 @@
         <v>3</v>
       </c>
       <c r="D22">
-        <v>43.215510000000002</v>
+        <v>43.256120000000003</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
@@ -1325,7 +1325,7 @@
         <v>3</v>
       </c>
       <c r="D23">
-        <v>42.098320000000001</v>
+        <v>42.141509999999997</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
@@ -1339,7 +1339,7 @@
         <v>3</v>
       </c>
       <c r="D24">
-        <v>41.07443</v>
+        <v>41.117440000000002</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
@@ -1353,7 +1353,7 @@
         <v>3</v>
       </c>
       <c r="D25">
-        <v>40.123980000000003</v>
+        <v>40.165059999999997</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="D26">
-        <v>39.233159999999998</v>
+        <v>39.27131</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
@@ -1381,7 +1381,7 @@
         <v>3</v>
       </c>
       <c r="D27">
-        <v>38.391620000000003</v>
+        <v>38.426609999999997</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
@@ -1395,7 +1395,7 @@
         <v>3</v>
       </c>
       <c r="D28">
-        <v>37.592619999999997</v>
+        <v>37.624369999999999</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
@@ -1409,7 +1409,7 @@
         <v>3</v>
       </c>
       <c r="D29">
-        <v>36.830680000000001</v>
+        <v>36.859650000000002</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
@@ -1423,7 +1423,7 @@
         <v>3</v>
       </c>
       <c r="D30">
-        <v>36.101390000000002</v>
+        <v>36.128279999999997</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
@@ -1437,7 +1437,7 @@
         <v>3</v>
       </c>
       <c r="D31">
-        <v>35.401420000000002</v>
+        <v>35.42671</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
@@ -1451,7 +1451,7 @@
         <v>3</v>
       </c>
       <c r="D32">
-        <v>34.726520000000001</v>
+        <v>34.750210000000003</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
@@ -1465,7 +1465,7 @@
         <v>3</v>
       </c>
       <c r="D33">
-        <v>34.074219999999997</v>
+        <v>34.096449999999997</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
@@ -1479,7 +1479,7 @@
         <v>3</v>
       </c>
       <c r="D34">
-        <v>33.442999999999998</v>
+        <v>33.464100000000002</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
@@ -1493,7 +1493,7 @@
         <v>3</v>
       </c>
       <c r="D35">
-        <v>32.832009999999997</v>
+        <v>32.853079999999999</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.4">
@@ -1507,7 +1507,7 @@
         <v>3</v>
       </c>
       <c r="D36">
-        <v>32.239849999999997</v>
+        <v>32.261279999999999</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
@@ -1521,7 +1521,7 @@
         <v>3</v>
       </c>
       <c r="D37">
-        <v>31.665489999999998</v>
+        <v>31.686540000000001</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>32.655679999999997</v>
+        <v>32.668210000000002</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.4">
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>33.482939999999999</v>
+        <v>33.49118</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.4">
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>34.197920000000003</v>
+        <v>34.203989999999997</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.4">
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>34.830860000000001</v>
+        <v>34.835790000000003</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.4">
@@ -1591,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>35.401139999999998</v>
+        <v>35.405369999999998</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.4">
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>35.920549999999999</v>
+        <v>35.92492</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.4">
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>36.397539999999999</v>
+        <v>36.403019999999998</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.4">
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>36.838740000000001</v>
+        <v>36.846060000000001</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.4">
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>37.250500000000002</v>
+        <v>37.258890000000001</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.4">
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>37.636299999999999</v>
+        <v>37.645049999999998</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.4">
@@ -1675,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>37.998649999999998</v>
+        <v>38.007429999999999</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.4">
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>38.339190000000002</v>
+        <v>38.349629999999998</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.4">
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>38.660089999999997</v>
+        <v>38.673139999999997</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.4">
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>38.963500000000003</v>
+        <v>38.979179999999999</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.4">
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>39.251809999999999</v>
+        <v>39.268709999999999</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.4">
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>39.526119999999999</v>
+        <v>39.54325</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.4">
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>39.78725</v>
+        <v>39.804549999999999</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.4">
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>40.03586</v>
+        <v>40.053989999999999</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.4">
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>40.272689999999997</v>
+        <v>40.292180000000002</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.4">
@@ -1801,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>40.498199999999997</v>
+        <v>40.519199999999998</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.4">
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>40.713140000000003</v>
+        <v>40.735639999999997</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.4">
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>40.918239999999997</v>
+        <v>40.942210000000003</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.4">
@@ -1843,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>41.114559999999997</v>
+        <v>41.139389999999999</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.4">
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>41.302329999999998</v>
+        <v>41.327500000000001</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.4">
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>41.481740000000002</v>
+        <v>41.506950000000003</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.4">
@@ -1885,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>41.652619999999999</v>
+        <v>41.678350000000002</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.4">
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>41.81561</v>
+        <v>41.842140000000001</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.4">
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>41.971350000000001</v>
+        <v>41.998849999999997</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.4">
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>42.12039</v>
+        <v>42.148969999999998</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.4">
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>42.26294</v>
+        <v>42.29269</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.4">
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>42.399740000000001</v>
+        <v>42.430169999999997</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.4">
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>42.531199999999998</v>
+        <v>42.56174</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.4">
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>42.65748</v>
+        <v>42.687800000000003</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.4">
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>42.778910000000003</v>
+        <v>42.809089999999998</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.4">
@@ -2011,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>42.895850000000003</v>
+        <v>42.92586</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.4">
@@ -2025,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>43.008589999999998</v>
+        <v>43.038330000000002</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.4">
@@ -2039,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>43.118009999999998</v>
+        <v>43.147669999999998</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.4">
@@ -2053,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>43.223979999999997</v>
+        <v>43.253749999999997</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.4">
@@ -2067,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>43.326590000000003</v>
+        <v>43.356610000000003</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.4">
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>43.42624</v>
+        <v>43.456420000000001</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.4">
@@ -2095,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>43.523099999999999</v>
+        <v>43.553280000000001</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.4">
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>43.617669999999997</v>
+        <v>43.647709999999996</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.4">
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>43.710329999999999</v>
+        <v>43.740209999999998</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.4">
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>43.801020000000001</v>
+        <v>43.830829999999999</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.4">
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>43.890059999999998</v>
+        <v>43.919969999999999</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.4">
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>43.97766</v>
+        <v>44.007730000000002</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.4">
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>44.063899999999997</v>
+        <v>44.094099999999997</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.4">
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>44.149610000000003</v>
+        <v>44.180010000000003</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.4">
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>44.234690000000001</v>
+        <v>44.2654</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.4">
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>44.319139999999997</v>
+        <v>44.350209999999997</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.4">
@@ -2235,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>44.403309999999998</v>
+        <v>44.434519999999999</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.4">
@@ -2249,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>44.487180000000002</v>
+        <v>44.51831</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.4">
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>44.57067</v>
+        <v>44.601869999999998</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.4">
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>44.653700000000001</v>
+        <v>44.685600000000001</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.4">
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>44.736350000000002</v>
+        <v>44.769419999999997</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.4">
@@ -2305,7 +2305,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>44.819240000000001</v>
+        <v>44.853259999999999</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.4">
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>44.902639999999998</v>
+        <v>44.936990000000002</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.4">
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>44.986379999999997</v>
+        <v>45.020560000000003</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.4">
@@ -2347,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>45.070569999999996</v>
+        <v>45.104199999999999</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.4">
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>45.155050000000003</v>
+        <v>45.188040000000001</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.4">
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>45.239649999999997</v>
+        <v>45.272080000000003</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.4">
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>45.323999999999998</v>
+        <v>45.356349999999999</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.4">
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>45.408110000000001</v>
+        <v>45.440660000000001</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.4">
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>45.491799999999998</v>
+        <v>45.524590000000003</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.4">
@@ -2431,7 +2431,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>45.574689999999997</v>
+        <v>45.607460000000003</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.4">
@@ -2445,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>45.656959999999998</v>
+        <v>45.689459999999997</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.4">
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>45.738660000000003</v>
+        <v>45.771169999999998</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.4">
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>45.819690000000001</v>
+        <v>45.852899999999998</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.4">
@@ -2487,7 +2487,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>45.899970000000003</v>
+        <v>45.934359999999998</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.4">
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>45.9803</v>
+        <v>46.015329999999999</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.4">
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>46.060870000000001</v>
+        <v>46.095869999999998</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.4">
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>46.141550000000002</v>
+        <v>46.176090000000002</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.4">
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>46.222880000000004</v>
+        <v>46.256349999999998</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.4">
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>46.304850000000002</v>
+        <v>46.336889999999997</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.4">
@@ -2571,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>46.38729</v>
+        <v>46.417929999999998</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.4">
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>46.469639999999998</v>
+        <v>46.500129999999999</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.4">
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>46.552199999999999</v>
+        <v>46.583159999999999</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.4">
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>46.635370000000002</v>
+        <v>46.666969999999999</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.4">
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>46.71942</v>
+        <v>46.751489999999997</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.4">
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>46.804009999999998</v>
+        <v>46.836460000000002</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.4">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>46.888550000000002</v>
+        <v>46.920949999999998</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.4">
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="D119">
-        <v>46.972749999999998</v>
+        <v>47.004660000000001</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.4">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>47.056690000000003</v>
+        <v>47.087829999999997</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.4">
@@ -2697,7 +2697,7 @@
         <v>3</v>
       </c>
       <c r="D121">
-        <v>45.591900000000003</v>
+        <v>45.630809999999997</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.4">
@@ -2711,7 +2711,7 @@
         <v>3</v>
       </c>
       <c r="D122">
-        <v>44.30789</v>
+        <v>44.35125</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.4">
@@ -2725,7 +2725,7 @@
         <v>3</v>
       </c>
       <c r="D123">
-        <v>43.151820000000001</v>
+        <v>43.197580000000002</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.4">
@@ -2739,7 +2739,7 @@
         <v>3</v>
       </c>
       <c r="D124">
-        <v>42.091119999999997</v>
+        <v>42.136539999999997</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.4">
@@ -2753,7 +2753,7 @@
         <v>3</v>
       </c>
       <c r="D125">
-        <v>41.105609999999999</v>
+        <v>41.148969999999998</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.4">
@@ -2767,7 +2767,7 @@
         <v>3</v>
       </c>
       <c r="D126">
-        <v>40.181469999999997</v>
+        <v>40.221769999999999</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.4">
@@ -2781,7 +2781,7 @@
         <v>3</v>
       </c>
       <c r="D127">
-        <v>39.308219999999999</v>
+        <v>39.345239999999997</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.4">
@@ -2795,7 +2795,7 @@
         <v>3</v>
       </c>
       <c r="D128">
-        <v>38.479019999999998</v>
+        <v>38.512700000000002</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.4">
@@ -2809,7 +2809,7 @@
         <v>3</v>
       </c>
       <c r="D129">
-        <v>37.688299999999998</v>
+        <v>37.719099999999997</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.4">
@@ -2823,7 +2823,7 @@
         <v>3</v>
       </c>
       <c r="D130">
-        <v>36.931570000000001</v>
+        <v>36.9602</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.4">
@@ -2837,7 +2837,7 @@
         <v>3</v>
       </c>
       <c r="D131">
-        <v>36.205410000000001</v>
+        <v>36.23236</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.4">
@@ -2851,7 +2851,7 @@
         <v>3</v>
       </c>
       <c r="D132">
-        <v>35.505510000000001</v>
+        <v>35.530790000000003</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.4">
@@ -2865,7 +2865,7 @@
         <v>3</v>
       </c>
       <c r="D133">
-        <v>34.829320000000003</v>
+        <v>34.853070000000002</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.4">
@@ -2879,7 +2879,7 @@
         <v>3</v>
       </c>
       <c r="D134">
-        <v>34.175269999999998</v>
+        <v>34.197830000000003</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.4">
@@ -2893,7 +2893,7 @@
         <v>3</v>
       </c>
       <c r="D135">
-        <v>33.542450000000002</v>
+        <v>33.564909999999998</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.4">
@@ -2907,7 +2907,7 @@
         <v>3</v>
       </c>
       <c r="D136">
-        <v>32.929400000000001</v>
+        <v>32.952159999999999</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.4">
@@ -2921,7 +2921,7 @@
         <v>3</v>
       </c>
       <c r="D137">
-        <v>32.335039999999999</v>
+        <v>32.357379999999999</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.4">
@@ -2935,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="D138">
-        <v>33.305979999999998</v>
+        <v>33.319760000000002</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.4">
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="D139">
-        <v>34.114609999999999</v>
+        <v>34.12406</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.4">
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="D140">
-        <v>34.811599999999999</v>
+        <v>34.818829999999998</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.4">
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="D141">
-        <v>35.427160000000001</v>
+        <v>35.433210000000003</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.4">
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="D142">
-        <v>35.98066</v>
+        <v>35.985979999999998</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.4">
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="D143">
-        <v>36.483890000000002</v>
+        <v>36.489310000000003</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.4">
@@ -3019,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="D144">
-        <v>36.945259999999998</v>
+        <v>36.951770000000003</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.4">
@@ -3033,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="D145">
-        <v>37.371400000000001</v>
+        <v>37.3797</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.4">
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="D146">
-        <v>37.768619999999999</v>
+        <v>37.77796</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.4">
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="D147">
-        <v>38.140389999999996</v>
+        <v>38.150069999999999</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.4">
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="D148">
-        <v>38.489220000000003</v>
+        <v>38.498899999999999</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.4">
@@ -3089,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="D149">
-        <v>38.81671</v>
+        <v>38.828029999999998</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.4">
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="D150">
-        <v>39.125030000000002</v>
+        <v>39.138930000000002</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.4">
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="D151">
-        <v>39.4163</v>
+        <v>39.4328</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.4">
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="D152">
-        <v>39.692889999999998</v>
+        <v>39.710590000000003</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.4">
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="D153">
-        <v>39.955910000000003</v>
+        <v>39.97381</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.4">
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="D154">
-        <v>40.206139999999998</v>
+        <v>40.224179999999997</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.4">
@@ -3173,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="D155">
-        <v>40.444229999999997</v>
+        <v>40.463090000000001</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.4">
@@ -3187,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="D156">
-        <v>40.670909999999999</v>
+        <v>40.691110000000002</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.4">
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="D157">
-        <v>40.886629999999997</v>
+        <v>40.908329999999999</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.4">
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="D158">
-        <v>41.092129999999997</v>
+        <v>41.115290000000002</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.4">
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="D159">
-        <v>41.288110000000003</v>
+        <v>41.312739999999998</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.4">
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="D160">
-        <v>41.475639999999999</v>
+        <v>41.501100000000001</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.4">
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="D161">
-        <v>41.654919999999997</v>
+        <v>41.680700000000002</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.4">
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="D162">
-        <v>41.826129999999999</v>
+        <v>41.851939999999999</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.4">
@@ -3285,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="D163">
-        <v>41.989100000000001</v>
+        <v>42.015419999999999</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.4">
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="D164">
-        <v>42.144460000000002</v>
+        <v>42.171559999999999</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.4">
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="D165">
-        <v>42.292830000000002</v>
+        <v>42.320889999999999</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.4">
@@ -3327,7 +3327,7 @@
         <v>0</v>
       </c>
       <c r="D166">
-        <v>42.434750000000001</v>
+        <v>42.463880000000003</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.4">
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="D167">
-        <v>42.570430000000002</v>
+        <v>42.600709999999999</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.4">
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="D168">
-        <v>42.700589999999998</v>
+        <v>42.731540000000003</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.4">
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="D169">
-        <v>42.825650000000003</v>
+        <v>42.856699999999996</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.4">
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="D170">
-        <v>42.945729999999998</v>
+        <v>42.976550000000003</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.4">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="D171">
-        <v>43.06118</v>
+        <v>43.091850000000001</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.4">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="D172">
-        <v>43.172350000000002</v>
+        <v>43.202829999999999</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.4">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="D173">
-        <v>43.279499999999999</v>
+        <v>43.309699999999999</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.4">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="D174">
-        <v>43.38353</v>
+        <v>43.413640000000001</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.4">
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="D175">
-        <v>43.484279999999998</v>
+        <v>43.514490000000002</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.4">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="D176">
-        <v>43.581850000000003</v>
+        <v>43.612299999999998</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.4">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="D177">
-        <v>43.676630000000003</v>
+        <v>43.707230000000003</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.4">
@@ -3495,7 +3495,7 @@
         <v>0</v>
       </c>
       <c r="D178">
-        <v>43.768770000000004</v>
+        <v>43.799370000000003</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.4">
@@ -3509,7 +3509,7 @@
         <v>0</v>
       </c>
       <c r="D179">
-        <v>43.858789999999999</v>
+        <v>43.889229999999998</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.4">
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="D180">
-        <v>43.947040000000001</v>
+        <v>43.977310000000003</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.4">
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="D181">
-        <v>44.033450000000002</v>
+        <v>44.063659999999999</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.4">
@@ -3551,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="D182">
-        <v>44.118369999999999</v>
+        <v>44.14866</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.4">
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="D183">
-        <v>44.201970000000003</v>
+        <v>44.232410000000002</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.4">
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="D184">
-        <v>44.28434</v>
+        <v>44.314909999999998</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.4">
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="D185">
-        <v>44.366309999999999</v>
+        <v>44.397069999999999</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.4">
@@ -3607,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="D186">
-        <v>44.447760000000002</v>
+        <v>44.478819999999999</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.4">
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="D187">
-        <v>44.528689999999997</v>
+        <v>44.560110000000002</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.4">
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="D188">
-        <v>44.609450000000002</v>
+        <v>44.640999999999998</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.4">
@@ -3649,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="D189">
-        <v>44.690019999999997</v>
+        <v>44.721490000000003</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.4">
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="D190">
-        <v>44.770310000000002</v>
+        <v>44.801839999999999</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.4">
@@ -3677,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="D191">
-        <v>44.850239999999999</v>
+        <v>44.882460000000002</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.4">
@@ -3691,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="D192">
-        <v>44.929879999999997</v>
+        <v>44.963270000000001</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.4">
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="D193">
-        <v>45.00985</v>
+        <v>45.044179999999997</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.4">
@@ -3719,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="D194">
-        <v>45.090420000000002</v>
+        <v>45.125079999999997</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.4">
@@ -3733,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="D195">
-        <v>45.171410000000002</v>
+        <v>45.205889999999997</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.4">
@@ -3747,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="D196">
-        <v>45.252929999999999</v>
+        <v>45.286859999999997</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.4">
@@ -3761,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="D197">
-        <v>45.334820000000001</v>
+        <v>45.368099999999998</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.4">
@@ -3775,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="D198">
-        <v>45.416899999999998</v>
+        <v>45.44961</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.4">
@@ -3789,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="D199">
-        <v>45.498809999999999</v>
+        <v>45.531440000000003</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.4">
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="D200">
-        <v>45.580539999999999</v>
+        <v>45.61336</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.4">
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="D201">
-        <v>45.661920000000002</v>
+        <v>45.694980000000001</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.4">
@@ -3831,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="D202">
-        <v>45.742570000000001</v>
+        <v>45.775599999999997</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.4">
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="D203">
-        <v>45.822650000000003</v>
+        <v>45.855420000000002</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.4">
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="D204">
-        <v>45.90222</v>
+        <v>45.934989999999999</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.4">
@@ -3873,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="D205">
-        <v>45.981189999999998</v>
+        <v>46.014650000000003</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.4">
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="D206">
-        <v>46.059460000000001</v>
+        <v>46.094099999999997</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.4">
@@ -3901,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="D207">
-        <v>46.137830000000001</v>
+        <v>46.173099999999998</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.4">
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="D208">
-        <v>46.21649</v>
+        <v>46.251730000000002</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.4">
@@ -3929,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="D209">
-        <v>46.295319999999997</v>
+        <v>46.330089999999998</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.4">
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="D210">
-        <v>46.374830000000003</v>
+        <v>46.408529999999999</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.4">
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="D211">
-        <v>46.455039999999997</v>
+        <v>46.487299999999998</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.4">
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="D212">
-        <v>46.53575</v>
+        <v>46.566630000000004</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.4">
@@ -3985,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="D213">
-        <v>46.616430000000001</v>
+        <v>46.64714</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.4">
@@ -3999,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="D214">
-        <v>46.69735</v>
+        <v>46.728529999999999</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.4">
@@ -4013,7 +4013,7 @@
         <v>0</v>
       </c>
       <c r="D215">
-        <v>46.778930000000003</v>
+        <v>46.810740000000003</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.4">
@@ -4027,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="D216">
-        <v>46.861429999999999</v>
+        <v>46.893709999999999</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.4">
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="D217">
-        <v>46.944499999999998</v>
+        <v>46.977150000000002</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.4">
@@ -4055,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="D218">
-        <v>47.027549999999998</v>
+        <v>47.06015</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.4">
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="D219">
-        <v>47.110300000000002</v>
+        <v>47.142409999999998</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.4">
@@ -4083,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="D220">
-        <v>47.192819999999998</v>
+        <v>47.224159999999998</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.4">
@@ -4097,7 +4097,7 @@
         <v>3</v>
       </c>
       <c r="D221">
-        <v>45.726669999999999</v>
+        <v>45.765779999999999</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.4">
@@ -4111,7 +4111,7 @@
         <v>3</v>
       </c>
       <c r="D222">
-        <v>44.441369999999999</v>
+        <v>44.484929999999999</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.4">
@@ -4125,7 +4125,7 @@
         <v>3</v>
       </c>
       <c r="D223">
-        <v>43.28407</v>
+        <v>43.330030000000001</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.4">
@@ -4139,7 +4139,7 @@
         <v>3</v>
       </c>
       <c r="D224">
-        <v>42.222189999999998</v>
+        <v>42.267809999999997</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.4">
@@ -4153,7 +4153,7 @@
         <v>3</v>
       </c>
       <c r="D225">
-        <v>41.23556</v>
+        <v>41.2791</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.4">
@@ -4167,7 +4167,7 @@
         <v>3</v>
       </c>
       <c r="D226">
-        <v>40.310319999999997</v>
+        <v>40.3508</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.4">
@@ -4181,7 +4181,7 @@
         <v>3</v>
       </c>
       <c r="D227">
-        <v>39.436019999999999</v>
+        <v>39.473219999999998</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.4">
@@ -4195,7 +4195,7 @@
         <v>3</v>
       </c>
       <c r="D228">
-        <v>38.605809999999998</v>
+        <v>38.639670000000002</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.4">
@@ -4209,7 +4209,7 @@
         <v>3</v>
       </c>
       <c r="D229">
-        <v>37.814109999999999</v>
+        <v>37.845080000000003</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.4">
@@ -4223,7 +4223,7 @@
         <v>3</v>
       </c>
       <c r="D230">
-        <v>37.056429999999999</v>
+        <v>37.085239999999999</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.4">
@@ -4237,7 +4237,7 @@
         <v>3</v>
       </c>
       <c r="D231">
-        <v>36.329349999999998</v>
+        <v>36.356470000000002</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.4">
@@ -4251,7 +4251,7 @@
         <v>3</v>
       </c>
       <c r="D232">
-        <v>35.62856</v>
+        <v>35.654000000000003</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.4">
@@ -4265,7 +4265,7 @@
         <v>3</v>
       </c>
       <c r="D233">
-        <v>34.951500000000003</v>
+        <v>34.97542</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.4">
@@ -4279,7 +4279,7 @@
         <v>3</v>
       </c>
       <c r="D234">
-        <v>34.296610000000001</v>
+        <v>34.319330000000001</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.4">
@@ -4293,7 +4293,7 @@
         <v>3</v>
       </c>
       <c r="D235">
-        <v>33.662959999999998</v>
+        <v>33.685589999999998</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.4">
@@ -4307,7 +4307,7 @@
         <v>3</v>
       </c>
       <c r="D236">
-        <v>33.049120000000002</v>
+        <v>33.072049999999997</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.4">
@@ -4321,7 +4321,7 @@
         <v>3</v>
       </c>
       <c r="D237">
-        <v>32.453980000000001</v>
+        <v>32.476480000000002</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.4">
@@ -4335,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="D238">
-        <v>33.424149999999997</v>
+        <v>33.438090000000003</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.4">
@@ -4349,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="D239">
-        <v>34.231990000000003</v>
+        <v>34.241599999999998</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.4">
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="D240">
-        <v>34.928179999999998</v>
+        <v>34.935569999999998</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.4">
@@ -4377,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="D241">
-        <v>35.542949999999998</v>
+        <v>35.549149999999997</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.4">
@@ -4391,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="D242">
-        <v>36.095649999999999</v>
+        <v>36.101129999999998</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.4">
@@ -4405,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="D243">
-        <v>36.598080000000003</v>
+        <v>36.603659999999998</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.4">
@@ -4419,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="D244">
-        <v>37.058660000000003</v>
+        <v>37.06532</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.4">
@@ -4433,7 +4433,7 @@
         <v>0</v>
       </c>
       <c r="D245">
-        <v>37.484009999999998</v>
+        <v>37.492460000000001</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.4">
@@ -4447,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="D246">
-        <v>37.880450000000003</v>
+        <v>37.889940000000003</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.4">
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="D247">
-        <v>38.251440000000002</v>
+        <v>38.261270000000003</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.4">
@@ -4475,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="D248">
-        <v>38.599490000000003</v>
+        <v>38.609319999999997</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.4">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="D249">
-        <v>38.926209999999998</v>
+        <v>38.937669999999997</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.4">
@@ -4503,7 +4503,7 @@
         <v>0</v>
       </c>
       <c r="D250">
-        <v>39.23377</v>
+        <v>39.247810000000001</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.4">
@@ -4517,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="D251">
-        <v>39.524279999999997</v>
+        <v>39.54092</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.4">
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="D252">
-        <v>39.800130000000003</v>
+        <v>39.817970000000003</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.4">
@@ -4545,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="D253">
-        <v>40.06241</v>
+        <v>40.080440000000003</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.4">
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="D254">
-        <v>40.311900000000001</v>
+        <v>40.330080000000002</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.4">
@@ -4573,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="D255">
-        <v>40.549259999999997</v>
+        <v>40.568249999999999</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.4">
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="D256">
-        <v>40.775230000000001</v>
+        <v>40.795549999999999</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.4">
@@ -4601,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="D257">
-        <v>40.990229999999997</v>
+        <v>41.012050000000002</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.4">
@@ -4615,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="D258">
-        <v>41.19502</v>
+        <v>41.218310000000002</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.4">
@@ -4629,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="D259">
-        <v>41.390309999999999</v>
+        <v>41.415059999999997</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.4">
@@ -4643,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="D260">
-        <v>41.577150000000003</v>
+        <v>41.602730000000001</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.4">
@@ -4657,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="D261">
-        <v>41.755740000000003</v>
+        <v>41.781649999999999</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.4">
@@ -4671,7 +4671,7 @@
         <v>0</v>
       </c>
       <c r="D262">
-        <v>41.926279999999998</v>
+        <v>41.952210000000001</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.4">
@@ -4685,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="D263">
-        <v>42.08858</v>
+        <v>42.115020000000001</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.4">
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="D264">
-        <v>42.243279999999999</v>
+        <v>42.270499999999998</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.4">
@@ -4713,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="D265">
-        <v>42.390999999999998</v>
+        <v>42.419170000000001</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.4">
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="D266">
-        <v>42.532269999999997</v>
+        <v>42.561520000000002</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.4">
@@ -4741,7 +4741,7 @@
         <v>0</v>
       </c>
       <c r="D267">
-        <v>42.667319999999997</v>
+        <v>42.697710000000001</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.4">
@@ -4755,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="D268">
-        <v>42.796849999999999</v>
+        <v>42.827910000000003</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.4">
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="D269">
-        <v>42.921280000000003</v>
+        <v>42.952440000000003</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.4">
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="D270">
-        <v>43.040750000000003</v>
+        <v>43.071680000000001</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.4">
@@ -4797,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="D271">
-        <v>43.155589999999997</v>
+        <v>43.186369999999997</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.4">
@@ -4811,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="D272">
-        <v>43.266159999999999</v>
+        <v>43.296750000000003</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.4">
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="D273">
-        <v>43.372720000000001</v>
+        <v>43.403019999999998</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.4">
@@ -4839,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="D274">
-        <v>43.476170000000003</v>
+        <v>43.506369999999997</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.4">
@@ -4853,7 +4853,7 @@
         <v>0</v>
       </c>
       <c r="D275">
-        <v>43.576329999999999</v>
+        <v>43.606650000000002</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.4">
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="D276">
-        <v>43.67333</v>
+        <v>43.703879999999998</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.4">
@@ -4881,7 +4881,7 @@
         <v>0</v>
       </c>
       <c r="D277">
-        <v>43.767539999999997</v>
+        <v>43.79824</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.4">
@@ -4895,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="D278">
-        <v>43.85913</v>
+        <v>43.88982</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.4">
@@ -4909,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="D279">
-        <v>43.948590000000003</v>
+        <v>43.979129999999998</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.4">
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="D280">
-        <v>44.036299999999997</v>
+        <v>44.066659999999999</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.4">
@@ -4937,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="D281">
-        <v>44.122169999999997</v>
+        <v>44.152459999999998</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.4">
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="D282">
-        <v>44.20655</v>
+        <v>44.236930000000001</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.4">
@@ -4965,7 +4965,7 @@
         <v>0</v>
       </c>
       <c r="D283">
-        <v>44.289630000000002</v>
+        <v>44.320160000000001</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.4">
@@ -4979,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="D284">
-        <v>44.371470000000002</v>
+        <v>44.40213</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.4">
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="D285">
-        <v>44.452919999999999</v>
+        <v>44.48377</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.4">
@@ -5007,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="D286">
-        <v>44.533859999999997</v>
+        <v>44.565010000000001</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.4">
@@ -5021,7 +5021,7 @@
         <v>0</v>
       </c>
       <c r="D287">
-        <v>44.614289999999997</v>
+        <v>44.645789999999998</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.4">
@@ -5035,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="D288">
-        <v>44.69455</v>
+        <v>44.726179999999999</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.4">
@@ -5049,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="D289">
-        <v>44.774630000000002</v>
+        <v>44.806170000000002</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.4">
@@ -5063,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="D290">
-        <v>44.854419999999998</v>
+        <v>44.886029999999998</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.4">
@@ -5077,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="D291">
-        <v>44.933869999999999</v>
+        <v>44.966169999999998</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.4">
@@ -5091,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="D292">
-        <v>45.013030000000001</v>
+        <v>45.046500000000002</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.4">
@@ -5105,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="D293">
-        <v>45.09252</v>
+        <v>45.126930000000002</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.4">
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="D294">
-        <v>45.172620000000002</v>
+        <v>45.207360000000001</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.4">
@@ -5133,7 +5133,7 @@
         <v>0</v>
       </c>
       <c r="D295">
-        <v>45.253149999999998</v>
+        <v>45.287700000000001</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.4">
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="D296">
-        <v>45.334209999999999</v>
+        <v>45.368209999999998</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.4">
@@ -5161,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="D297">
-        <v>45.415640000000003</v>
+        <v>45.448990000000002</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.4">
@@ -5175,7 +5175,7 @@
         <v>0</v>
       </c>
       <c r="D298">
-        <v>45.49727</v>
+        <v>45.530050000000003</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.4">
@@ -5189,7 +5189,7 @@
         <v>0</v>
       </c>
       <c r="D299">
-        <v>45.578719999999997</v>
+        <v>45.611429999999999</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.4">
@@ -5203,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="D300">
-        <v>45.66001</v>
+        <v>45.692900000000002</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.4">
@@ -5217,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="D301">
-        <v>45.740949999999998</v>
+        <v>45.774079999999998</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.4">
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="D302">
-        <v>45.821159999999999</v>
+        <v>45.85427</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.4">
@@ -5245,7 +5245,7 @@
         <v>0</v>
       </c>
       <c r="D303">
-        <v>45.90081</v>
+        <v>45.933639999999997</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/data_symbols_TD/06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5.xlsx
+++ b/inputs/data_symbols_TD/06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54C6E577-4E36-43D0-BF7E-F78810A78116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A558050D-4698-4BEC-A102-854363B4CFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{318F9C05-CB7A-4F9A-B260-76030DFDF66D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{6F9BE058-9DCC-4EC6-81ED-E46CE1E7FBA1}"/>
   </bookViews>
   <sheets>
     <sheet name="06_LTAN06_800km_1213COLD_PX_STT" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0162C8EE-22EF-4229-B1FC-ABF5E6DC8A15}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A05FCB-F903-442A-8A9E-2691A4082173}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/inputs/data_symbols_TD/06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5.xlsx
+++ b/inputs/data_symbols_TD/06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A558050D-4698-4BEC-A102-854363B4CFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5936341E-66F4-4578-BA45-300C5B3A1F00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{6F9BE058-9DCC-4EC6-81ED-E46CE1E7FBA1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{C46B3F33-07D0-4452-AD39-F1AF97E520D8}"/>
   </bookViews>
   <sheets>
     <sheet name="06_LTAN06_800km_1213COLD_PX_STT" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A05FCB-F903-442A-8A9E-2691A4082173}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE480CC3-6204-4338-A2B1-6B147535A5D1}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
